--- a/cls.var_AMR_ES_C3G_R.xlsx
+++ b/cls.var_AMR_ES_C3G_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -62,6 +62,9 @@
     <t xml:space="preserve">log_AMC_ville_macrolides</t>
   </si>
   <si>
+    <t xml:space="preserve">cluster_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">log_AMC_ville_penicillines</t>
   </si>
   <si>
@@ -80,6 +83,9 @@
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
   </si>
   <si>
+    <t xml:space="preserve">prescri_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">AMR_animaux_production_C3G_R</t>
   </si>
   <si>
@@ -108,9 +114,6 @@
   </si>
   <si>
     <t xml:space="preserve">log_UGB_density_lapins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cluster_4</t>
   </si>
   <si>
     <t xml:space="preserve">log_UGB_density_livestock_tot</t>
@@ -575,7 +578,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -583,36 +586,36 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
         <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
@@ -620,7 +623,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -628,23 +631,23 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -652,31 +655,31 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
@@ -684,15 +687,15 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
@@ -700,7 +703,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
@@ -708,10 +711,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -719,7 +722,7 @@
         <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -735,7 +738,7 @@
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -743,7 +746,7 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
@@ -751,7 +754,7 @@
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -759,7 +762,7 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -775,7 +778,7 @@
         <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -783,7 +786,7 @@
         <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -791,7 +794,7 @@
         <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -807,7 +810,7 @@
         <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
@@ -831,7 +834,7 @@
         <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -847,6 +850,14 @@
         <v>49</v>
       </c>
       <c r="B45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" t="s">
         <v>6</v>
       </c>
     </row>
